--- a/modelo-importacao-demandas.xlsx
+++ b/modelo-importacao-demandas.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A34C053-C957-41D4-83A3-D35F322F2925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DA42DD-FEE3-43E3-8420-AF92C4E6104C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>Demanda</t>
   </si>
@@ -48,12 +48,6 @@
     <t>Observações</t>
   </si>
   <si>
-    <t>Evolutiva</t>
-  </si>
-  <si>
-    <t>Backlog</t>
-  </si>
-  <si>
     <t>Campo</t>
   </si>
   <si>
@@ -96,55 +90,37 @@
     <t>Informações complementares.</t>
   </si>
   <si>
-    <t>[OXXO] Integrar filiais do SAP para Frete</t>
-  </si>
-  <si>
-    <t>Q3 &gt; Q4</t>
-  </si>
-  <si>
-    <t>Gerenciamento de transmissões</t>
-  </si>
-  <si>
-    <t>Estratégia 2026. Influencia diretamente na meta de redução de chamados</t>
-  </si>
-  <si>
-    <t>Sincronização de ocorrência parametrizáveis (Move)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Impacto GEQ - Verificar Elog</t>
-  </si>
-  <si>
-    <t>Tem paliativo</t>
-  </si>
-  <si>
-    <t>Tratar performance e telas lentas</t>
-  </si>
-  <si>
-    <t>* Estratégia 2026. Influencia diretamente na meta de redução de chamados</t>
-  </si>
-  <si>
-    <t>Analisar componentes que impedem seleção</t>
-  </si>
-  <si>
-    <t>Penske</t>
-  </si>
-  <si>
-    <t>Atualizar componentes NDS</t>
-  </si>
-  <si>
-    <t>Operador e Embarcador - Segurança</t>
-  </si>
-  <si>
-    <t>nddFrete</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Estratégica</t>
-  </si>
-  <si>
-    <t>Incidente</t>
+    <t>Alterar autorização CIOT NDD Tech &gt; IP</t>
+  </si>
+  <si>
+    <t>Migração Dock → NDD IP (Onda 2)</t>
+  </si>
+  <si>
+    <t>Redução de Chamados e Incidentes (top 10 causas raízes)</t>
+  </si>
+  <si>
+    <t>Revisão Login Portal</t>
+  </si>
+  <si>
+    <t>nddCargo</t>
+  </si>
+  <si>
+    <t>Regulatória</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfação </t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Em Andamento</t>
   </si>
 </sst>
 </file>
@@ -196,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -207,6 +183,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -548,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -596,182 +575,96 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>31</v>
+      </c>
+      <c r="G2" s="6">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G3" s="6">
+        <v>700</v>
+      </c>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G4" s="6">
+        <v>300</v>
+      </c>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>38</v>
+      <c r="G5" s="6">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C501" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2 D2:D490" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"Baixa,Média,Alta,Crítica"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C490" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Estratégica,Evolutiva,Bug,Incidente,Sustentação,Regulatória,Técnica,Emergencial"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D501" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"Baixa,Média,Alta,Crítica"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E501" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E3:E490" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Backlog,Planejada,Em análise,Desenvolvimento,Em testes,Homologação,Concluída,Cancelada,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -792,13 +685,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,10 +710,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -828,10 +721,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,10 +732,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +743,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +754,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,10 +765,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -883,10 +776,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -894,10 +787,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +798,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/modelo-importacao-demandas.xlsx
+++ b/modelo-importacao-demandas.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DA42DD-FEE3-43E3-8420-AF92C4E6104C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Demandas" sheetId="1" r:id="rId1"/>
-    <sheet name="Instruções" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Demandas" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Instruções" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
   <si>
     <t>Demanda</t>
   </si>
@@ -88,57 +87,24 @@
   </si>
   <si>
     <t>Informações complementares.</t>
-  </si>
-  <si>
-    <t>Alterar autorização CIOT NDD Tech &gt; IP</t>
-  </si>
-  <si>
-    <t>Migração Dock → NDD IP (Onda 2)</t>
-  </si>
-  <si>
-    <t>Redução de Chamados e Incidentes (top 10 causas raízes)</t>
-  </si>
-  <si>
-    <t>Revisão Login Portal</t>
-  </si>
-  <si>
-    <t>nddCargo</t>
-  </si>
-  <si>
-    <t>Regulatória</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satisfação </t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Em Andamento</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -172,8 +138,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -182,12 +151,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,171 +489,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="22" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="2" customWidth="1"/>
     <col min="8" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="6">
-        <v>700</v>
-      </c>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="6">
-        <v>300</v>
-      </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="6">
-        <v>50</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="E2 D2:D490" xr:uid="{00000000-0002-0000-0000-000002000000}">
+  <autoFilter ref="A1:J1"/>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C490">
+      <formula1>"Estratégica,Evolutiva,Bug,Incidente,Sustentação,Regulatória,Técnica,Emergencial"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C490">
+      <formula1>"Estratégica,Evolutiva,Bug,Incidente,Sustentação,Regulatória,Técnica,Emergencial"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D490">
       <formula1>"Baixa,Média,Alta,Crítica"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C490" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Estratégica,Evolutiva,Bug,Incidente,Sustentação,Regulatória,Técnica,Emergencial"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D490">
+      <formula1>"Baixa,Média,Alta,Crítica"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E3:E490" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E490">
+      <formula1>"Backlog,Planejada,Em análise,Desenvolvimento,Em testes,Homologação,Concluída,Cancelada,Bloqueada"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E2">
+      <formula1>"Baixa,Média,Alta,Crítica"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E3:E490">
       <formula1>"Backlog,Planejada,Em análise,Desenvolvimento,Em testes,Homologação,Concluída,Cancelada,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -806,6 +699,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>